--- a/data/Diessenhofen/investment_decision/Willisdorf_SFH_until_2004_investment_decision.xlsx
+++ b/data/Diessenhofen/investment_decision/Willisdorf_SFH_until_2004_investment_decision.xlsx
@@ -470,22 +470,22 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>2.782232000000005</v>
+        <v>32.46771112701928</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -508,19 +508,19 @@
         <v>38298.90664300384</v>
       </c>
       <c r="F2" t="n">
-        <v>2.782232000000005</v>
+        <v>32.95006367334501</v>
       </c>
       <c r="G2" t="n">
         <v>38298.90664300384</v>
       </c>
       <c r="H2" t="n">
-        <v>2.782232000000004</v>
+        <v>29.68852895328566</v>
       </c>
       <c r="I2" t="n">
         <v>38298.90664300384</v>
       </c>
       <c r="J2" t="n">
-        <v>2.782232000000004</v>
+        <v>26.00590133830725</v>
       </c>
       <c r="K2" t="n">
         <v>38298.90664300384</v>
@@ -531,7 +531,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>51.19007605609239</v>
+        <v>47.08102277762681</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -545,19 +545,19 @@
         <v>38298.90664300384</v>
       </c>
       <c r="F3" t="n">
-        <v>52.55209630923478</v>
+        <v>47.67674757925499</v>
       </c>
       <c r="G3" t="n">
         <v>38298.90664300384</v>
       </c>
       <c r="H3" t="n">
-        <v>52.86914666666666</v>
+        <v>45.95356224047344</v>
       </c>
       <c r="I3" t="n">
         <v>38298.90664300384</v>
       </c>
       <c r="J3" t="n">
-        <v>51.52950000000001</v>
+        <v>41.73010224591047</v>
       </c>
       <c r="K3" t="n">
         <v>38298.90664300384</v>
@@ -568,7 +568,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>86.01906396213452</v>
+        <v>66.66725261329826</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,19 +582,19 @@
         <v>38298.90664300384</v>
       </c>
       <c r="F4" t="n">
-        <v>86.01906396213452</v>
+        <v>68.09157517788248</v>
       </c>
       <c r="G4" t="n">
         <v>38298.90664300384</v>
       </c>
       <c r="H4" t="n">
-        <v>86.01906396213454</v>
+        <v>66.70029525127418</v>
       </c>
       <c r="I4" t="n">
         <v>38298.90664300384</v>
       </c>
       <c r="J4" t="n">
-        <v>86.01906396213454</v>
+        <v>68.17769842216084</v>
       </c>
       <c r="K4" t="n">
         <v>38298.90664300384</v>
@@ -605,7 +605,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>196.9928800823929</v>
+        <v>206.1070086369886</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -619,19 +619,19 @@
         <v>38298.90664300384</v>
       </c>
       <c r="F5" t="n">
-        <v>182.1147891837689</v>
+        <v>203.2605787086904</v>
       </c>
       <c r="G5" t="n">
         <v>38298.90664300384</v>
       </c>
       <c r="H5" t="n">
-        <v>168.7617388120945</v>
+        <v>205.7249009086429</v>
       </c>
       <c r="I5" t="n">
         <v>38298.90664300384</v>
       </c>
       <c r="J5" t="n">
-        <v>163.3439304073965</v>
+        <v>202.9461355497951</v>
       </c>
       <c r="K5" t="n">
         <v>38298.90664300384</v>
@@ -642,7 +642,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>196.9928800823929</v>
+        <v>206.1070086369886</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -656,19 +656,19 @@
         <v>38298.90664300384</v>
       </c>
       <c r="F6" t="n">
-        <v>182.1147891837689</v>
+        <v>203.2605787086904</v>
       </c>
       <c r="G6" t="n">
         <v>38298.90664300384</v>
       </c>
       <c r="H6" t="n">
-        <v>168.7617388120945</v>
+        <v>205.7249009086429</v>
       </c>
       <c r="I6" t="n">
         <v>38298.90664300384</v>
       </c>
       <c r="J6" t="n">
-        <v>163.3439304073965</v>
+        <v>202.9461355497951</v>
       </c>
       <c r="K6" t="n">
         <v>38298.90664300384</v>
@@ -683,32 +683,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Willisdorf_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Willisdorf_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>57.44835996450577</v>
+        <v>48.63458426966292</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>57.44835996450577</v>
+        <v>48.63458426966292</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>33.54422914804896</v>
+        <v>28.39784530436779</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>33.54422914804896</v>
+        <v>28.39784530436779</v>
       </c>
     </row>
     <row r="8">
@@ -720,32 +720,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Willisdorf_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Willisdorf_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>57.44835996450577</v>
+        <v>48.63458426966292</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>57.44835996450577</v>
+        <v>48.63458426966292</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>44.52210084680801</v>
+        <v>37.69148269566521</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>44.52210084680801</v>
+        <v>37.69148269566521</v>
       </c>
     </row>
     <row r="9">
@@ -757,32 +757,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Willisdorf_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Willisdorf_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>57.44835996450577</v>
+        <v>48.63458426966292</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>57.44835996450577</v>
+        <v>48.63458426966292</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>49.31598911379103</v>
+        <v>41.74988859348343</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>49.31598911379103</v>
+        <v>41.74988859348343</v>
       </c>
     </row>
     <row r="10">
@@ -794,32 +794,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Willisdorf_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Willisdorf_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>57.44835996450577</v>
+        <v>48.63458426966292</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>57.44835996450577</v>
+        <v>48.63458426966292</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>51.80767752511259</v>
+        <v>43.85930007344617</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>51.80767752511259</v>
+        <v>43.85930007344617</v>
       </c>
     </row>
     <row r="11">
@@ -831,32 +831,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Willisdorf_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Willisdorf_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>57.44835996450577</v>
+        <v>48.63458426966292</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>57.44835996450577</v>
+        <v>48.63458426966292</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>53.2606039745373</v>
+        <v>45.08931732521501</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>53.2606039745373</v>
+        <v>45.08931732521501</v>
       </c>
     </row>
     <row r="12">
@@ -864,7 +864,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.007529369294117646</v>
+        <v>0.005892549882352942</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -878,19 +878,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.007529369294117646</v>
+        <v>0.005892549882352942</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.007529369294117646</v>
+        <v>0.005991899138823529</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.007529369294117647</v>
+        <v>0.00653363225522966</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -901,7 +901,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.007529369294117646</v>
+        <v>0.006301744117647057</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -915,19 +915,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.007529369294117646</v>
+        <v>0.006473085230588235</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.007529369294117646</v>
+        <v>0.006547277647058823</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.007529369294117646</v>
+        <v>0.006547277647058823</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -938,7 +938,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.008838824823529415</v>
+        <v>0.007202005411764707</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,19 +952,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.008838824823529415</v>
+        <v>0.007349778005849555</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.008838824823529415</v>
+        <v>0.007347052720537472</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.008838824823529415</v>
+        <v>0.007414621625280777</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -975,7 +975,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.008838824823529415</v>
+        <v>0.007555443122095688</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,19 +989,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.008838824823529415</v>
+        <v>0.007529369294117646</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.008838824823529415</v>
+        <v>0.007529369294117226</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.008838824823529415</v>
+        <v>0.007529369294117646</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1012,7 +1012,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.008838824823529415</v>
+        <v>0.007555443122095701</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1026,19 +1026,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.008838824823529415</v>
+        <v>0.007529369294117705</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.008838824823529415</v>
+        <v>0.007529369294117226</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.008838824823529415</v>
+        <v>0.007611199647058827</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1086,7 +1086,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>0.8244756907252211</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1100,19 +1100,19 @@
         <v>5.8434453</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.7988590016583512</v>
       </c>
       <c r="G18" t="n">
         <v>5.8434453</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.8636348654951016</v>
       </c>
       <c r="I18" t="n">
         <v>5.8434453</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.9130326875000001</v>
       </c>
       <c r="K18" t="n">
         <v>5.8434453</v>
@@ -1123,7 +1123,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1.506272219611882</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,19 +1137,19 @@
         <v>5.8434453</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1.494507251658323</v>
       </c>
       <c r="G19" t="n">
         <v>5.8434453</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1.559283115495327</v>
       </c>
       <c r="I19" t="n">
         <v>5.8434453</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1.5652085625</v>
       </c>
       <c r="K19" t="n">
         <v>5.8434453</v>
@@ -1160,7 +1160,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1.506272219611882</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,19 +1174,19 @@
         <v>5.8434453</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1.494507251658323</v>
       </c>
       <c r="G20" t="n">
         <v>5.8434453</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1.559283115495327</v>
       </c>
       <c r="I20" t="n">
         <v>5.8434453</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1.5652085625</v>
       </c>
       <c r="K20" t="n">
         <v>5.8434453</v>
@@ -1197,7 +1197,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>0.6817965288866606</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,19 +1211,19 @@
         <v>5.8434453</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.6956482499999713</v>
       </c>
       <c r="G21" t="n">
         <v>5.8434453</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.6956482500002251</v>
       </c>
       <c r="I21" t="n">
         <v>5.8434453</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.6521758749999997</v>
       </c>
       <c r="K21" t="n">
         <v>5.8434453</v>
@@ -2344,7 +2344,7 @@
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>7.125950045011127</v>
+        <v>7.577610368980991</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2358,19 +2358,19 @@
         <v>56.90637133582118</v>
       </c>
       <c r="F52" t="n">
-        <v>6.745503985333338</v>
+        <v>7.113333918388883</v>
       </c>
       <c r="G52" t="n">
         <v>56.90637133582118</v>
       </c>
       <c r="H52" t="n">
-        <v>6.577843216395538</v>
+        <v>6.591725420054884</v>
       </c>
       <c r="I52" t="n">
         <v>19.09487805645101</v>
       </c>
       <c r="J52" t="n">
-        <v>5.720729056558878</v>
+        <v>6.795413676132881</v>
       </c>
       <c r="K52" t="n">
         <v>19.09487805645101</v>
@@ -2381,7 +2381,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>7.125950045011127</v>
+        <v>7.577610368980991</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2395,19 +2395,19 @@
         <v>56.90637133582118</v>
       </c>
       <c r="F53" t="n">
-        <v>6.745503985333338</v>
+        <v>7.113333918388883</v>
       </c>
       <c r="G53" t="n">
         <v>56.90637133582118</v>
       </c>
       <c r="H53" t="n">
-        <v>6.577843216395538</v>
+        <v>6.591725420054884</v>
       </c>
       <c r="I53" t="n">
         <v>28.83442812654594</v>
       </c>
       <c r="J53" t="n">
-        <v>5.720729056558878</v>
+        <v>6.795413676132881</v>
       </c>
       <c r="K53" t="n">
         <v>28.83442812654594</v>
@@ -2418,7 +2418,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>13.55536888042908</v>
+        <v>12.08525654803009</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2432,19 +2432,19 @@
         <v>56.90637133582118</v>
       </c>
       <c r="F54" t="n">
-        <v>13.17492282075129</v>
+        <v>12.02436390085303</v>
       </c>
       <c r="G54" t="n">
         <v>56.90637133582118</v>
       </c>
       <c r="H54" t="n">
-        <v>13.00726205181349</v>
+        <v>11.36174874387581</v>
       </c>
       <c r="I54" t="n">
         <v>34.49412653418358</v>
       </c>
       <c r="J54" t="n">
-        <v>12.15014789197683</v>
+        <v>12.02068195937574</v>
       </c>
       <c r="K54" t="n">
         <v>34.49412653418358</v>
@@ -2455,7 +2455,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>14.46355454958775</v>
+        <v>14.6687568483799</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2469,19 +2469,19 @@
         <v>56.90637133582118</v>
       </c>
       <c r="F55" t="n">
-        <v>13.96755054818256</v>
+        <v>14.38277383706597</v>
       </c>
       <c r="G55" t="n">
         <v>56.90637133582118</v>
       </c>
       <c r="H55" t="n">
-        <v>13.69112658912459</v>
+        <v>14.66755691390967</v>
       </c>
       <c r="I55" t="n">
         <v>38.10515862924322</v>
       </c>
       <c r="J55" t="n">
-        <v>14.29468302015504</v>
+        <v>14.34216742965929</v>
       </c>
       <c r="K55" t="n">
         <v>38.10515862924322</v>
@@ -2492,7 +2492,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>14.46355454958775</v>
+        <v>14.6687568483799</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2506,19 +2506,19 @@
         <v>56.90637133582118</v>
       </c>
       <c r="F56" t="n">
-        <v>13.96755054818257</v>
+        <v>14.38277383706597</v>
       </c>
       <c r="G56" t="n">
         <v>56.90637133582118</v>
       </c>
       <c r="H56" t="n">
-        <v>13.69112658912459</v>
+        <v>14.66755691390967</v>
       </c>
       <c r="I56" t="n">
         <v>40.56781088496604</v>
       </c>
       <c r="J56" t="n">
-        <v>14.29468302015504</v>
+        <v>14.34216742965929</v>
       </c>
       <c r="K56" t="n">
         <v>40.56781088496604</v>
@@ -2714,7 +2714,7 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>11.34853063047892</v>
+        <v>10.92585744366975</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2728,19 +2728,19 @@
         <v>56.90637133582118</v>
       </c>
       <c r="F62" t="n">
-        <v>11.7579638273174</v>
+        <v>11.39013389426185</v>
       </c>
       <c r="G62" t="n">
         <v>56.90637133582118</v>
       </c>
       <c r="H62" t="n">
-        <v>11.9256245962552</v>
+        <v>11.16461333083463</v>
       </c>
       <c r="I62" t="n">
         <v>56.90637133582118</v>
       </c>
       <c r="J62" t="n">
-        <v>11.32338896915885</v>
+        <v>11.70805413651786</v>
       </c>
       <c r="K62" t="n">
         <v>56.90637133582118</v>
@@ -2751,7 +2751,7 @@
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>11.34853063047892</v>
+        <v>10.92585744366975</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2765,19 +2765,19 @@
         <v>56.90637133582118</v>
       </c>
       <c r="F63" t="n">
-        <v>11.7579638273174</v>
+        <v>11.39013389426185</v>
       </c>
       <c r="G63" t="n">
         <v>56.90637133582118</v>
       </c>
       <c r="H63" t="n">
-        <v>11.9256245962552</v>
+        <v>11.16461333083463</v>
       </c>
       <c r="I63" t="n">
         <v>56.90637133582118</v>
       </c>
       <c r="J63" t="n">
-        <v>11.32338896915885</v>
+        <v>11.70805413651786</v>
       </c>
       <c r="K63" t="n">
         <v>56.90637133582118</v>
@@ -2788,7 +2788,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>11.34853063047892</v>
+        <v>10.92585744366975</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2802,19 +2802,19 @@
         <v>56.90637133582118</v>
       </c>
       <c r="F64" t="n">
-        <v>11.7579638273174</v>
+        <v>11.39013389426185</v>
       </c>
       <c r="G64" t="n">
         <v>56.90637133582118</v>
       </c>
       <c r="H64" t="n">
-        <v>11.9256245962552</v>
+        <v>11.16461333083463</v>
       </c>
       <c r="I64" t="n">
         <v>56.90637133582118</v>
       </c>
       <c r="J64" t="n">
-        <v>11.32338896915885</v>
+        <v>11.70805413651786</v>
       </c>
       <c r="K64" t="n">
         <v>56.90637133582118</v>
@@ -2825,7 +2825,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>8.02138027229878</v>
+        <v>1.68160395309015</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2839,19 +2839,19 @@
         <v>56.90637133582118</v>
       </c>
       <c r="F65" t="n">
-        <v>8.845577455291258</v>
+        <v>2.048160435505134</v>
       </c>
       <c r="G65" t="n">
         <v>56.90637133582118</v>
       </c>
       <c r="H65" t="n">
-        <v>9.416553996077342</v>
+        <v>1.69461025983178</v>
       </c>
       <c r="I65" t="n">
         <v>56.90637133582118</v>
       </c>
       <c r="J65" t="n">
-        <v>8.932508044562296</v>
+        <v>2.097541403228829</v>
       </c>
       <c r="K65" t="n">
         <v>56.90637133582118</v>
@@ -2862,7 +2862,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>8.02138027229878</v>
+        <v>1.681603953090148</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2876,19 +2876,19 @@
         <v>56.90637133582118</v>
       </c>
       <c r="F66" t="n">
-        <v>8.845577455291258</v>
+        <v>2.048160435505134</v>
       </c>
       <c r="G66" t="n">
         <v>56.90637133582118</v>
       </c>
       <c r="H66" t="n">
-        <v>9.416553996077342</v>
+        <v>1.69461025983178</v>
       </c>
       <c r="I66" t="n">
         <v>56.90637133582118</v>
       </c>
       <c r="J66" t="n">
-        <v>8.932508044562296</v>
+        <v>2.097541403228829</v>
       </c>
       <c r="K66" t="n">
         <v>56.90637133582118</v>
@@ -3107,13 +3107,13 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>2.267017753005788</v>
+        <v>56.90637133582118</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>2.267017753005788</v>
+        <v>56.90637133582118</v>
       </c>
     </row>
     <row r="73">
@@ -3144,13 +3144,13 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>3.883220521615061</v>
+        <v>56.90637133582118</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>3.883220521615061</v>
+        <v>56.90637133582118</v>
       </c>
     </row>
     <row r="74">
@@ -3181,13 +3181,13 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>5.158400180709886</v>
+        <v>56.90637133582118</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>5.158400180709886</v>
+        <v>56.90637133582118</v>
       </c>
     </row>
     <row r="75">
@@ -3218,13 +3218,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>6.218378998000898</v>
+        <v>56.90637133582118</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>6.218378998000898</v>
+        <v>56.90637133582118</v>
       </c>
     </row>
     <row r="76">
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>7.127398345388347</v>
+        <v>56.90637133582118</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>7.127398345388347</v>
+        <v>56.90637133582118</v>
       </c>
     </row>
     <row r="77">
@@ -3269,7 +3269,7 @@
         <v>46023</v>
       </c>
       <c r="B77" t="n">
-        <v>0.02898713716069123</v>
+        <v>0</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3289,16 +3289,16 @@
         <v>56.90637133582118</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>0.7471290617612267</v>
       </c>
       <c r="I77" t="n">
-        <v>2.267017753005788</v>
+        <v>56.90637133582118</v>
       </c>
       <c r="J77" t="n">
-        <v>1.459349786933011</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>2.267017753005788</v>
+        <v>56.90637133582118</v>
       </c>
     </row>
     <row r="78">
@@ -3306,7 +3306,7 @@
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>0.02898713716069123</v>
+        <v>0</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3326,16 +3326,16 @@
         <v>56.90637133582118</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>0.7471290617612267</v>
       </c>
       <c r="I78" t="n">
-        <v>3.883220521615061</v>
+        <v>56.90637133582118</v>
       </c>
       <c r="J78" t="n">
-        <v>1.459349786933011</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>3.883220521615061</v>
+        <v>56.90637133582118</v>
       </c>
     </row>
     <row r="79">
@@ -3343,7 +3343,7 @@
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>0.02898713716069123</v>
+        <v>0</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3363,16 +3363,16 @@
         <v>56.90637133582118</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>0.7471290617612267</v>
       </c>
       <c r="I79" t="n">
-        <v>5.158400180709886</v>
+        <v>56.90637133582118</v>
       </c>
       <c r="J79" t="n">
-        <v>1.459349786933011</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>5.158400180709886</v>
+        <v>56.90637133582118</v>
       </c>
     </row>
     <row r="80">
@@ -3403,13 +3403,13 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>6.218378998000898</v>
+        <v>56.90637133582118</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>6.218378998000898</v>
+        <v>56.90637133582118</v>
       </c>
     </row>
     <row r="81">
@@ -3440,13 +3440,13 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>7.127398345388347</v>
+        <v>56.90637133582118</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>7.127398345388347</v>
+        <v>56.90637133582118</v>
       </c>
     </row>
     <row r="82">
